--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92566863536</v>
+        <v>46157.93093984255</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93093984255</v>
+        <v>46157.93170969493</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93170969493</v>
+        <v>46157.93398688557</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93398688557</v>
+        <v>46157.93716431259</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93716431259</v>
+        <v>46158.2821504856</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2821504856</v>
+        <v>46158.29676535187</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29676535187</v>
+        <v>46158.2981313727</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.2981313727</v>
+        <v>46158.33386005999</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33386005999</v>
+        <v>46158.36855780616</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/23. Сибкар Центр (ремонт автомобиля 054)/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36855780616</v>
+        <v>46158.37286499286</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
